--- a/培训日报/培训专用测试点文件夹/无畏契约冲分活动测试点/测试用例示例.xlsx
+++ b/培训日报/培训专用测试点文件夹/无畏契约冲分活动测试点/测试用例示例.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Student\Notes\Obsidian-Notes\培训日报\培训专用测试点文件夹\无畏契约冲分活动测试点\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2F24AA3-2689-49E0-8607-600086624508}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64E82547-93A6-4B93-9D84-E4B7BDE01816}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{84964265-8865-4634-8B81-646B51793405}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="40">
   <si>
     <t>用例编号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -79,10 +79,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>去活动中心查看活动是否开启</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>活动开启，活动中心出现入口</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -140,6 +136,62 @@
   </si>
   <si>
     <t>任务状态为：已领取</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>点赞对象</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>有添加一个游戏好友</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>和游戏好友完成一把对局，结束后他对我进行点赞</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>游戏好友点赞会被记数，点赞次数+1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>有添加一个平台好友</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>和平台好友完成一把对局，结束后他对我进行点赞</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>平台好友点赞会被记数，点赞次数+1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>无需和任何好友组队</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>和陌生玩家完成一把对局，结束后某玩家对我进行点赞</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>对局陌生玩家点赞会被记数，点赞次数+1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>点赞</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>修改服务器时间到2.15 23：59：59</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>进入游戏，去活动中心查看活动是否开放</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>修改服务器时间到2.16 00：00：01</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -215,7 +267,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -223,6 +275,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -539,13 +594,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5E80E7A-8C9F-4C2A-A28C-AE1487C4EFC5}">
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="39.109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="33.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="29.21875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="53.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="40.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -617,6 +673,17 @@
         <v>8</v>
       </c>
     </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="D10" t="s">
+        <v>37</v>
+      </c>
+      <c r="E10" t="s">
+        <v>38</v>
+      </c>
+      <c r="F10" t="s">
+        <v>11</v>
+      </c>
+    </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>9</v>
@@ -625,70 +692,131 @@
         <v>10</v>
       </c>
       <c r="D11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E11" t="s">
+        <v>38</v>
+      </c>
+      <c r="F11" t="s">
         <v>11</v>
       </c>
-      <c r="F11" t="s">
-        <v>12</v>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="D12" t="s">
+        <v>39</v>
+      </c>
+      <c r="E12" t="s">
+        <v>38</v>
+      </c>
+      <c r="F12" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C15" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
-        <v>14</v>
-      </c>
-      <c r="C16" t="s">
+        <v>13</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D16" t="s">
+        <v>18</v>
+      </c>
+      <c r="E16" t="s">
+        <v>21</v>
+      </c>
+      <c r="F16" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C17" s="3"/>
+      <c r="D17" t="s">
+        <v>18</v>
+      </c>
+      <c r="E17" t="s">
+        <v>19</v>
+      </c>
+      <c r="F17" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C18" s="3"/>
+      <c r="D18" t="s">
+        <v>23</v>
+      </c>
+      <c r="E18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F18" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="20" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C20" t="s">
         <v>16</v>
       </c>
-      <c r="D16" t="s">
-        <v>19</v>
-      </c>
-      <c r="E16" t="s">
-        <v>22</v>
-      </c>
-      <c r="F16" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="17" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D17" t="s">
-        <v>19</v>
-      </c>
-      <c r="E17" t="s">
-        <v>20</v>
-      </c>
-      <c r="F17" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="18" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="D18" t="s">
-        <v>24</v>
-      </c>
-      <c r="E18" t="s">
-        <v>25</v>
-      </c>
-      <c r="F18" t="s">
+    </row>
+    <row r="23" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C23" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="26" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B26" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C26" s="3" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="20" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C20" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="23" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C23" t="s">
-        <v>18</v>
+      <c r="D26" t="s">
+        <v>27</v>
+      </c>
+      <c r="E26" t="s">
+        <v>28</v>
+      </c>
+      <c r="F26" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B27" s="3"/>
+      <c r="C27" s="3"/>
+      <c r="D27" t="s">
+        <v>30</v>
+      </c>
+      <c r="E27" t="s">
+        <v>31</v>
+      </c>
+      <c r="F27" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="28" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B28" s="3"/>
+      <c r="C28" s="3"/>
+      <c r="D28" t="s">
+        <v>33</v>
+      </c>
+      <c r="E28" t="s">
+        <v>34</v>
+      </c>
+      <c r="F28" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="C16:C18"/>
+    <mergeCell ref="C26:C28"/>
+    <mergeCell ref="B26:B28"/>
+  </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="0" orientation="portrait" horizontalDpi="0" verticalDpi="0" copies="0"/>

--- a/培训日报/培训专用测试点文件夹/无畏契约冲分活动测试点/测试用例示例.xlsx
+++ b/培训日报/培训专用测试点文件夹/无畏契约冲分活动测试点/测试用例示例.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Student\Notes\Obsidian-Notes\培训日报\培训专用测试点文件夹\无畏契约冲分活动测试点\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64E82547-93A6-4B93-9D84-E4B7BDE01816}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32F4AF86-E049-40D4-BCD4-E02389BBCA78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{84964265-8865-4634-8B81-646B51793405}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="46">
   <si>
     <t>用例编号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -192,6 +192,30 @@
   </si>
   <si>
     <t>修改服务器时间到2.16 00：00：01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>奖励领取</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>登录领取状态</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>领取奖励异常测试</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>把手机网络调成弱网环境，且完成任务条件</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>点击领取奖励</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>奖励正常领取，正常到账</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -267,7 +291,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -279,6 +303,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -594,12 +621,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5E80E7A-8C9F-4C2A-A28C-AE1487C4EFC5}">
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I38"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="16.109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="39.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="33.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="42.44140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="53.44140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="40.5546875" bestFit="1" customWidth="1"/>
   </cols>
@@ -811,11 +838,47 @@
         <v>35</v>
       </c>
     </row>
+    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B33" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C33" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="34" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B34" s="4"/>
+    </row>
+    <row r="35" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B35" s="4"/>
+    </row>
+    <row r="36" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B36" s="4"/>
+    </row>
+    <row r="37" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B37" s="4"/>
+    </row>
+    <row r="38" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B38" s="4"/>
+      <c r="C38" t="s">
+        <v>42</v>
+      </c>
+      <c r="D38" t="s">
+        <v>43</v>
+      </c>
+      <c r="E38" t="s">
+        <v>44</v>
+      </c>
+      <c r="F38" t="s">
+        <v>45</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="C16:C18"/>
     <mergeCell ref="C26:C28"/>
     <mergeCell ref="B26:B28"/>
+    <mergeCell ref="B33:B38"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/培训日报/培训专用测试点文件夹/无畏契约冲分活动测试点/测试用例示例.xlsx
+++ b/培训日报/培训专用测试点文件夹/无畏契约冲分活动测试点/测试用例示例.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Student\Notes\Obsidian-Notes\培训日报\培训专用测试点文件夹\无畏契约冲分活动测试点\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32F4AF86-E049-40D4-BCD4-E02389BBCA78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A923678-4C10-4109-8EB1-6E4EF60758AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{84964265-8865-4634-8B81-646B51793405}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="53">
   <si>
     <t>用例编号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -217,6 +217,33 @@
   <si>
     <t>奖励正常领取，正常到账</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>应援投票</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>应援投票异常测试</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>进入活动界面</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>同时点击三个应援按钮</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>弹出一个弹窗</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>P0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>P1</t>
   </si>
 </sst>
 </file>
@@ -621,7 +648,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5E80E7A-8C9F-4C2A-A28C-AE1487C4EFC5}">
-  <dimension ref="A1:I38"/>
+  <dimension ref="A1:I43"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="16.109375" bestFit="1" customWidth="1"/>
@@ -664,43 +691,70 @@
       <c r="A2">
         <v>1</v>
       </c>
+      <c r="H2" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
+      <c r="H3" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
+      <c r="H4" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
+      <c r="H5" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
+      <c r="H6" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
+      <c r="H7" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
+      <c r="H8" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
+      <c r="H9" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C10" s="3" t="s">
+        <v>10</v>
+      </c>
       <c r="D10" t="s">
         <v>37</v>
       </c>
@@ -709,15 +763,16 @@
       </c>
       <c r="F10" t="s">
         <v>11</v>
+      </c>
+      <c r="H10" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>9</v>
       </c>
-      <c r="C11" t="s">
-        <v>10</v>
-      </c>
+      <c r="C11" s="3"/>
       <c r="D11" t="s">
         <v>12</v>
       </c>
@@ -727,8 +782,12 @@
       <c r="F11" t="s">
         <v>11</v>
       </c>
+      <c r="H11" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C12" s="3"/>
       <c r="D12" t="s">
         <v>39</v>
       </c>
@@ -737,6 +796,9 @@
       </c>
       <c r="F12" t="s">
         <v>11</v>
+      </c>
+      <c r="H12" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
@@ -873,14 +935,50 @@
         <v>45</v>
       </c>
     </row>
+    <row r="40" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B40" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C40" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="41" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B41" s="4"/>
+    </row>
+    <row r="42" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B42" s="4"/>
+    </row>
+    <row r="43" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B43" s="4"/>
+      <c r="C43" t="s">
+        <v>47</v>
+      </c>
+      <c r="D43" t="s">
+        <v>48</v>
+      </c>
+      <c r="E43" t="s">
+        <v>49</v>
+      </c>
+      <c r="F43" t="s">
+        <v>50</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="6">
     <mergeCell ref="C16:C18"/>
     <mergeCell ref="C26:C28"/>
     <mergeCell ref="B26:B28"/>
     <mergeCell ref="B33:B38"/>
+    <mergeCell ref="B40:B43"/>
+    <mergeCell ref="C10:C12"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2:H28" xr:uid="{E8FCF440-D8BB-48CC-B466-7823E31FCE69}">
+      <formula1>"P0,P1,P2,P3"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="0" orientation="portrait" horizontalDpi="0" verticalDpi="0" copies="0"/>
 </worksheet>

--- a/培训日报/培训专用测试点文件夹/无畏契约冲分活动测试点/测试用例示例.xlsx
+++ b/培训日报/培训专用测试点文件夹/无畏契约冲分活动测试点/测试用例示例.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Student\Notes\Obsidian-Notes\培训日报\培训专用测试点文件夹\无畏契约冲分活动测试点\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A923678-4C10-4109-8EB1-6E4EF60758AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A402CEF-B764-429C-8150-E85348D43E30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{84964265-8865-4634-8B81-646B51793405}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="10.26" sheetId="1" r:id="rId1"/>
+    <sheet name="10.27" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="148">
   <si>
     <t>用例编号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -244,13 +245,393 @@
   </si>
   <si>
     <t>P1</t>
+  </si>
+  <si>
+    <t>次数刷新清空规则</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用限制段位校验</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>第二次无消耗</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>当日排位赛胜利2局，查看是否可消耗</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>有双倍加分次数2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用规则-消耗限制</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>胜利后自动消耗</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>排位赛首胜一局，查看次数消耗方式</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>有双倍加分次数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用规则-消耗方式</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>消耗成功，次数-1，积分增加</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>查看次数消耗清空</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>活动期间进入排位赛首胜一局</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用规则-参与玩法</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>双倍加分使用规则</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>页面显示数据正常</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>进入每日首胜页面，查看数据</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>完成任务并已领取</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>奖励到账</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>任务可一件领奖，任务奖励领奖正常</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>进入活动点击领取</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>活动期间内有多个以上任务完成</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>活动期间内有1个任务完成</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>领奖方式-一键领取</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>任务可以单独领奖，任务奖励领奖正常</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>活动期间有1个任务完成</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>领奖方式-单独领奖</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>奖励为1次加分次数，ICON名称，数量正常</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>进入活动查看累计登录任务奖励</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>活动期间已登录游戏</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>任务奖励的配置-累计对局任务</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>任务奖励的配置-累计登录任务</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>任务奖励</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>是否刷新？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>进入活动查看任务状态刷新</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>修改服务器时间到xxxxxx</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试任务刷新时间</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>活动登录任务刷新</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>可以完成任务</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>选择排位模式，多人胜利一局</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>活动期间内进入活动大厅</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>选择排位模式，单人胜利一局</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>累计对局任务-任务参与人数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>任务进度未1/6，数据不变</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.16选择排位模式，胜利一句后退出客户端</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>活动期间未完成任务</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>累计对局任务-任务进度持久化测试</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>任务进度6/6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2.18选择排位/普通模式，胜利6局</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>任务进度5/6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2.18选择排位/普通模式，胜利5局</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>任务进度4/6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2.17选择排位/普通模式，胜利4局</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>任务进度3/6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2.17选择排位/普通模式，胜利3局</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>任务进度2/6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2.16选择排位/普通模式，胜利2局</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>任务进度1/6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2.16选择排位/普通模式，胜利一局</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>累计对局任务-任务进度展示</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>无法完成任务</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>选择排位/普通模式，平局一局</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>活动期间进入对战大厅</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>选择排位/普通模式，失败一局</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>可完成任务</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>选择排位/普通模式，胜利一局</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>累计对局任务-胜负条件</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>选择自定义，胜利一局</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>选择娱乐模式，胜利一句</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>选择普通模式，胜利一局</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>选择排位模式，胜利一局</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>累计对局任务-任务参与模式</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>跳转至对战大厅</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>进入活动点击按钮</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>活动期间内未完成任务条件</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>累计对局任务-前往按钮跳转功能测试</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>任务状态为“已领取”</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>进入活动查看任务状态</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>活动期间内完成任务条件</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>任务状态为“领取”</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>任务状态为“前往”</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>后台查看任务状态</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>活动期间内未完成任务</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>累计对局任务-任务状态</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>任务进度变为1/1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>进入活动查看任务进度</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>累计登录任务进度展示</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>进入活动领取奖励</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>累计登录任务-已完成任务状态</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>进入活动后查看任务状态</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>任务状态为未完成</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>后天查看任务状态</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>活动期间未登录游戏</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>累计登录任务-未完成任务状态</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>活动任务</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -274,8 +655,24 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -285,6 +682,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -318,7 +721,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -333,6 +736,24 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -966,12 +1387,12 @@
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="C10:C12"/>
     <mergeCell ref="C16:C18"/>
     <mergeCell ref="C26:C28"/>
     <mergeCell ref="B26:B28"/>
     <mergeCell ref="B33:B38"/>
     <mergeCell ref="B40:B43"/>
-    <mergeCell ref="C10:C12"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="1">
@@ -982,4 +1403,570 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="0" orientation="portrait" horizontalDpi="0" verticalDpi="0" copies="0"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5DE766C-887D-406E-B516-8527961DD88F}">
+  <dimension ref="A1:I51"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="36.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="30.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="41.77734375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="42" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.21875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" s="8" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="A1" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B6" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B7" s="7"/>
+      <c r="C7" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B8" s="7"/>
+      <c r="C8" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B9" s="7"/>
+      <c r="C9" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B10" s="7"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B11" s="7"/>
+      <c r="C11" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B12" s="7"/>
+      <c r="C12" s="7"/>
+      <c r="D12" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B13" s="7"/>
+      <c r="C13" s="7"/>
+      <c r="D13" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B14" s="7"/>
+      <c r="C14" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B15" s="7"/>
+      <c r="C15" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B16" s="7"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="17" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B17" s="7"/>
+      <c r="C17" s="7"/>
+      <c r="D17" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B18" s="7"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B19" s="7"/>
+      <c r="C19" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="20" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B20" s="7"/>
+      <c r="C20" s="7"/>
+      <c r="D20" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="21" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B21" s="7"/>
+      <c r="C21" s="7"/>
+      <c r="D21" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="22" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B22" s="7"/>
+      <c r="C22" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="23" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B23" s="7"/>
+      <c r="C23" s="7"/>
+      <c r="D23" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="24" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B24" s="7"/>
+      <c r="C24" s="7"/>
+      <c r="D24" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="25" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B25" s="7"/>
+      <c r="C25" s="7"/>
+      <c r="D25" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="26" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B26" s="7"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B27" s="7"/>
+      <c r="C27" s="7"/>
+      <c r="D27" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B28" s="7"/>
+      <c r="C28" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="F28" s="5" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="29" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B29" s="7"/>
+      <c r="C29" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B30" s="7"/>
+      <c r="C30" s="7"/>
+      <c r="D30" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="F30" s="5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="31" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B31" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="36" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B36" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C36" t="s">
+        <v>84</v>
+      </c>
+      <c r="D36" t="s">
+        <v>82</v>
+      </c>
+      <c r="E36" t="s">
+        <v>81</v>
+      </c>
+      <c r="F36" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="37" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B37" s="3"/>
+      <c r="C37" t="s">
+        <v>83</v>
+      </c>
+      <c r="D37" t="s">
+        <v>82</v>
+      </c>
+      <c r="E37" t="s">
+        <v>81</v>
+      </c>
+      <c r="F37" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="38" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B38" s="3"/>
+      <c r="C38" t="s">
+        <v>79</v>
+      </c>
+      <c r="D38" t="s">
+        <v>78</v>
+      </c>
+      <c r="E38" t="s">
+        <v>73</v>
+      </c>
+      <c r="F38" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="39" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B39" s="3"/>
+      <c r="C39" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D39" t="s">
+        <v>75</v>
+      </c>
+      <c r="E39" t="s">
+        <v>73</v>
+      </c>
+      <c r="F39" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="40" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B40" s="3"/>
+      <c r="C40" s="3"/>
+      <c r="D40" t="s">
+        <v>74</v>
+      </c>
+      <c r="E40" t="s">
+        <v>73</v>
+      </c>
+      <c r="F40" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="41" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B41" s="3"/>
+      <c r="C41" t="s">
+        <v>71</v>
+      </c>
+      <c r="D41" t="s">
+        <v>70</v>
+      </c>
+      <c r="E41" t="s">
+        <v>69</v>
+      </c>
+      <c r="F41" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="43" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B43" t="s">
+        <v>67</v>
+      </c>
+      <c r="C43" t="s">
+        <v>66</v>
+      </c>
+      <c r="D43" t="s">
+        <v>65</v>
+      </c>
+      <c r="E43" t="s">
+        <v>64</v>
+      </c>
+      <c r="F43" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="44" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C44" t="s">
+        <v>62</v>
+      </c>
+      <c r="D44" t="s">
+        <v>61</v>
+      </c>
+      <c r="E44" t="s">
+        <v>60</v>
+      </c>
+      <c r="F44" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="45" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C45" t="s">
+        <v>58</v>
+      </c>
+      <c r="D45" t="s">
+        <v>57</v>
+      </c>
+      <c r="E45" t="s">
+        <v>56</v>
+      </c>
+      <c r="F45" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="47" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C47" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="51" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C51" t="s">
+        <v>53</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="C39:C40"/>
+    <mergeCell ref="B36:B41"/>
+    <mergeCell ref="B6:B30"/>
+    <mergeCell ref="C11:C13"/>
+    <mergeCell ref="C15:C18"/>
+    <mergeCell ref="C19:C21"/>
+    <mergeCell ref="C22:C27"/>
+    <mergeCell ref="C29:C30"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>